--- a/Table/Excel/Item.xlsx
+++ b/Table/Excel/Item.xlsx
@@ -1,17 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <workbookPr defaultThemeVersion="166925"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TokTak\Desktop\Local\Unity\LOTW\LOTW\Table\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{27954D78-C9BF-4D64-B54F-17E0C7D87B7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{35518A88-0317-48A7-9E0F-C9981C476B9C}"/>
+  </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Item" state="visible" r:id="rId4"/>
+    <sheet name="Item" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="11">
   <si>
     <t>DataId</t>
   </si>
@@ -29,6 +43,12 @@
   </si>
   <si>
     <t>MaxStack</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>string</t>
   </si>
   <si>
     <t>rose</t>
@@ -43,14 +63,30 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
+      <charset val="129"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <name val="Calibri"/>
+      <color rgb="FF808080"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -71,15 +107,41 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="5">
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -93,29 +155,22 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" name="ItemTable" displayName="ItemTable" ref="A1:F2" totalsRowShown="1" headerRowCount="1">
-  <autoFilter ref="A1:F2">
-    <filterColumn colId="0" hiddenButton="0"/>
-    <filterColumn colId="1" hiddenButton="0"/>
-    <filterColumn colId="2" hiddenButton="0"/>
-    <filterColumn colId="3" hiddenButton="0"/>
-    <filterColumn colId="4" hiddenButton="0"/>
-    <filterColumn colId="5" hiddenButton="0"/>
-  </autoFilter>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{EDE1D533-195C-433F-93DA-44E8B5A38EF4}" name="Item" displayName="Item" ref="B2:G4" totalsRowShown="0" headerRowDxfId="0">
+  <autoFilter ref="B2:G4" xr:uid="{EDE1D533-195C-433F-93DA-44E8B5A38EF4}"/>
   <tableColumns count="6">
-    <tableColumn id="1" name="DataId" totalsRowLabel="Total"/>
-    <tableColumn id="2" name="ItemId" totalsRowFunction="none"/>
-    <tableColumn id="3" name="DisplayName" totalsRowFunction="none"/>
-    <tableColumn id="4" name="Description" totalsRowFunction="none"/>
-    <tableColumn id="5" name="Icon" totalsRowFunction="none"/>
-    <tableColumn id="6" name="MaxStack" totalsRowFunction="none"/>
+    <tableColumn id="1" xr3:uid="{0CEF135A-7C6A-4058-B43F-3893FC2AEBD6}" name="DataId"/>
+    <tableColumn id="2" xr3:uid="{2B3C629D-6877-48BF-859C-B96F10DBAA4D}" name="ItemId" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{75FB7605-B48E-434B-B845-C688E83ECBF4}" name="DisplayName" dataDxfId="3"/>
+    <tableColumn id="4" xr3:uid="{1F4D0055-347C-4927-B405-CDC1DDCFE2A5}" name="Description" dataDxfId="2"/>
+    <tableColumn id="5" xr3:uid="{061A01EB-5EF4-4D68-80A8-120D62CF9241}" name="Icon" dataDxfId="1"/>
+    <tableColumn id="6" xr3:uid="{7C5CEC00-8932-4FDC-A01E-F3E67DF23E17}" name="MaxStack"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -125,44 +180,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="800080"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线 Light"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -190,14 +245,31 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -225,6 +297,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -236,257 +325,219 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="35000">
-              <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="100000"/>
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
                 <a:shade val="100000"/>
-                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:shade val="100000"/>
-                <a:satMod val="350000"/>
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
+                <a:alpha val="63000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="40000">
-              <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:spDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="3">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </a:style>
-    </a:spDef>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD1E2E40-A28E-4B47-B3DD-72519159B69A}">
+  <dimension ref="B2:G4"/>
+  <sheetFormatPr defaultRowHeight="16.5" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8" customWidth="1"/>
-    <col min="2" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="24" customWidth="1"/>
-    <col min="5" max="5" width="20" customWidth="1"/>
-    <col min="6" max="6" width="10" customWidth="1"/>
+    <col min="1" max="1" width="3.125" customWidth="1"/>
+    <col min="2" max="2" width="9.625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="2" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2">
+    <row r="3" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B4">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="C4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F2">
+      <c r="D4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4">
         <v>99</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>

--- a/Table/Excel/Item.xlsx
+++ b/Table/Excel/Item.xlsx
@@ -1,97 +1,49 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TokTak\Desktop\Local\Unity\LOTW\LOTW\Table\Excel\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{27954D78-C9BF-4D64-B54F-17E0C7D87B7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{35518A88-0317-48A7-9E0F-C9981C476B9C}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Item" sheetId="1" r:id="rId1"/>
+    <sheet name="Item" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="11">
-  <si>
-    <t>DataId</t>
-  </si>
-  <si>
-    <t>ItemId</t>
-  </si>
-  <si>
-    <t>DisplayName</t>
-  </si>
-  <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>Icon</t>
-  </si>
-  <si>
-    <t>MaxStack</t>
-  </si>
-  <si>
-    <t>int</t>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>rose</t>
-  </si>
-  <si>
-    <t>@item.rose.name</t>
-  </si>
-  <si>
-    <t>@item.rose.desc</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="3">
     <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="2"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="맑은 고딕"/>
-      <family val="2"/>
-      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="2"/>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
-      <family val="2"/>
-      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="2"/>
+      <color rgb="FF808080"/>
       <sz val="11"/>
-      <color rgb="FF808080"/>
-      <name val="맑은 고딕"/>
-      <family val="2"/>
-      <charset val="129"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -107,20 +59,22 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+  <cellXfs count="5">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -143,27 +97,87 @@
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{EDE1D533-195C-433F-93DA-44E8B5A38EF4}" name="Item" displayName="Item" ref="B2:G4" totalsRowShown="0" headerRowDxfId="0">
-  <autoFilter ref="B2:G4" xr:uid="{EDE1D533-195C-433F-93DA-44E8B5A38EF4}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Item" displayName="Item" ref="B2:G10" headerRowCount="1" totalsRowShown="0" headerRowDxfId="0">
+  <autoFilter ref="B2:G10"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{0CEF135A-7C6A-4058-B43F-3893FC2AEBD6}" name="DataId"/>
-    <tableColumn id="2" xr3:uid="{2B3C629D-6877-48BF-859C-B96F10DBAA4D}" name="ItemId" dataDxfId="4"/>
-    <tableColumn id="3" xr3:uid="{75FB7605-B48E-434B-B845-C688E83ECBF4}" name="DisplayName" dataDxfId="3"/>
-    <tableColumn id="4" xr3:uid="{1F4D0055-347C-4927-B405-CDC1DDCFE2A5}" name="Description" dataDxfId="2"/>
-    <tableColumn id="5" xr3:uid="{061A01EB-5EF4-4D68-80A8-120D62CF9241}" name="Icon" dataDxfId="1"/>
-    <tableColumn id="6" xr3:uid="{7C5CEC00-8932-4FDC-A01E-F3E67DF23E17}" name="MaxStack"/>
+    <tableColumn id="1" name="DataId"/>
+    <tableColumn id="2" name="ItemId" dataDxfId="4"/>
+    <tableColumn id="3" name="DisplayName" dataDxfId="3"/>
+    <tableColumn id="4" name="Description" dataDxfId="2"/>
+    <tableColumn id="5" name="Icon" dataDxfId="1"/>
+    <tableColumn id="6" name="MaxStack"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -465,81 +479,259 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD1E2E40-A28E-4B47-B3DD-72519159B69A}">
-  <dimension ref="B2:G4"/>
-  <sheetFormatPr defaultRowHeight="16.5" customHeight="1" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:G10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="3.125" customWidth="1"/>
-    <col min="2" max="2" width="9.625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.125" bestFit="1" customWidth="1"/>
+    <col width="3.125" customWidth="1" style="3" min="1" max="1"/>
+    <col width="9.625" bestFit="1" customWidth="1" style="3" min="2" max="2"/>
+    <col width="9.625" bestFit="1" customWidth="1" style="1" min="3" max="3"/>
+    <col width="16.75" bestFit="1" customWidth="1" style="1" min="4" max="4"/>
+    <col width="15.625" bestFit="1" customWidth="1" style="1" min="5" max="5"/>
+    <col width="7.5" bestFit="1" customWidth="1" style="1" min="6" max="6"/>
+    <col width="12.125" bestFit="1" customWidth="1" style="3" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="1" t="s">
+    <row r="2" ht="16.5" customHeight="1" s="3">
+      <c r="B2" s="0" t="inlineStr">
+        <is>
+          <t>DataId</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>ItemId</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>DisplayName</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="F2" s="1" t="inlineStr">
+        <is>
+          <t>Icon</t>
+        </is>
+      </c>
+      <c r="G2" s="0" t="inlineStr">
+        <is>
+          <t>MaxStack</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="16.5" customHeight="1" s="3">
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="16.5" customHeight="1" s="3">
+      <c r="B4" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>rose</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="inlineStr">
+        <is>
+          <t>@item.rose.name</t>
+        </is>
+      </c>
+      <c r="E4" s="1" t="inlineStr">
+        <is>
+          <t>@item.rose.desc</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="n"/>
+      <c r="G4" s="0" t="n">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="n">
         <v>2</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>drink_soda</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>@item.drink_soda.name</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>@item.drink_soda.desc</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="n"/>
+      <c r="G5" t="n">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="n">
         <v>3</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>drink_milk</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>@item.drink_milk.name</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>@item.drink_milk.desc</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="n"/>
+      <c r="G6" t="n">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="n">
         <v>4</v>
       </c>
-      <c r="G2" t="s">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>drink_coffee</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>@item.drink_coffee.name</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>@item.drink_coffee.desc</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="n"/>
+      <c r="G7" t="n">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="n">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="2" t="s">
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>drink_lemon</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>@item.drink_lemon.name</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>@item.drink_lemon.desc</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="n"/>
+      <c r="G8" t="n">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="n">
         <v>6</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>drink_greentea</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>@item.drink_greentea.name</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>@item.drink_greentea.desc</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="n"/>
+      <c r="G9" t="n">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="n">
         <v>7</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G4">
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>drink_dud</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>@item.drink_dud.name</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>@item.drink_dud.desc</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="n"/>
+      <c r="G10" t="n">
         <v>99</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>